--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1591,6 +1591,732 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125847855</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>533951</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6596095</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125848524</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58186</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>533994</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6596007</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125848529</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58325</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>534002</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6596110</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125847854</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58365</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>533952</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6596094</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125847641</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>533982</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6596121</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125847639</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>533992</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6596062</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B12" t="n">
-        <v>58325</v>
+        <v>58365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R12" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58365</v>
+        <v>58325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R13" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1597,7 +1597,7 @@
         <v>125847855</v>
       </c>
       <c r="B10" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125848524</v>
       </c>
       <c r="B11" t="n">
-        <v>58186</v>
+        <v>58187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B12" t="n">
-        <v>58365</v>
+        <v>58326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R12" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B13" t="n">
-        <v>58325</v>
+        <v>58366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R13" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2081,7 @@
         <v>125847641</v>
       </c>
       <c r="B14" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B12" t="n">
-        <v>58326</v>
+        <v>58366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R12" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58366</v>
+        <v>58326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R13" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1715,32 +1715,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125848524</v>
+        <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58187</v>
+        <v>58366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533994</v>
+        <v>533952</v>
       </c>
       <c r="R11" t="n">
-        <v>6596007</v>
+        <v>6596094</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125847854</v>
+        <v>125848524</v>
       </c>
       <c r="B12" t="n">
-        <v>58366</v>
+        <v>58187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533952</v>
+        <v>533994</v>
       </c>
       <c r="R12" t="n">
-        <v>6596094</v>
+        <v>6596007</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1715,32 +1715,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125847854</v>
+        <v>125848524</v>
       </c>
       <c r="B11" t="n">
-        <v>58366</v>
+        <v>58187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533952</v>
+        <v>533994</v>
       </c>
       <c r="R11" t="n">
-        <v>6596094</v>
+        <v>6596007</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125848524</v>
+        <v>125847854</v>
       </c>
       <c r="B12" t="n">
-        <v>58187</v>
+        <v>58366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533994</v>
+        <v>533952</v>
       </c>
       <c r="R12" t="n">
-        <v>6596007</v>
+        <v>6596094</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1597,7 +1597,7 @@
         <v>125847855</v>
       </c>
       <c r="B10" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125848524</v>
       </c>
       <c r="B11" t="n">
-        <v>58187</v>
+        <v>58188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>125847854</v>
       </c>
       <c r="B12" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>125847641</v>
       </c>
       <c r="B14" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>125847639</v>
       </c>
       <c r="B15" t="n">
-        <v>57824</v>
+        <v>57825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B12" t="n">
-        <v>58367</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R12" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B13" t="n">
-        <v>58327</v>
+        <v>58367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R13" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>58367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R12" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,39 +1950,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58367</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R13" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1597,7 +1597,7 @@
         <v>125847855</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125848524</v>
       </c>
       <c r="B11" t="n">
-        <v>58188</v>
+        <v>58192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B12" t="n">
-        <v>58367</v>
+        <v>58331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R12" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B13" t="n">
-        <v>58327</v>
+        <v>58371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R13" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2081,7 @@
         <v>125847641</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
         <v>125847639</v>
       </c>
       <c r="B15" t="n">
-        <v>57825</v>
+        <v>57829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1715,32 +1715,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125848524</v>
+        <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58192</v>
+        <v>58371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533994</v>
+        <v>533952</v>
       </c>
       <c r="R11" t="n">
-        <v>6596007</v>
+        <v>6596094</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125847854</v>
+        <v>125848524</v>
       </c>
       <c r="B13" t="n">
-        <v>58371</v>
+        <v>58192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533952</v>
+        <v>533994</v>
       </c>
       <c r="R13" t="n">
-        <v>6596094</v>
+        <v>6596007</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1708,39 +1708,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125847854</v>
+        <v>125848524</v>
       </c>
       <c r="B11" t="n">
-        <v>58371</v>
+        <v>58192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533952</v>
+        <v>533994</v>
       </c>
       <c r="R11" t="n">
-        <v>6596094</v>
+        <v>6596007</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,39 +1829,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B12" t="n">
-        <v>58331</v>
+        <v>58371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R12" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,17 +1950,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125848524</v>
+        <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58192</v>
+        <v>58331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533994</v>
+        <v>534002</v>
       </c>
       <c r="R13" t="n">
-        <v>6596007</v>
+        <v>6596110</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1597,7 +1597,7 @@
         <v>125847855</v>
       </c>
       <c r="B10" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125848524</v>
       </c>
       <c r="B11" t="n">
-        <v>58192</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,32 +1836,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B12" t="n">
-        <v>58371</v>
+        <v>58334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R12" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125848529</v>
+        <v>125847854</v>
       </c>
       <c r="B13" t="n">
-        <v>58331</v>
+        <v>58374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534002</v>
+        <v>533952</v>
       </c>
       <c r="R13" t="n">
-        <v>6596110</v>
+        <v>6596094</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2081,7 @@
         <v>125847641</v>
       </c>
       <c r="B14" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>125847639</v>
       </c>
       <c r="B15" t="n">
-        <v>57829</v>
+        <v>57830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1715,32 +1715,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125848524</v>
+        <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533994</v>
+        <v>533952</v>
       </c>
       <c r="R11" t="n">
-        <v>6596007</v>
+        <v>6596094</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125848529</v>
+        <v>125848524</v>
       </c>
       <c r="B12" t="n">
-        <v>58334</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,16 +1847,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534002</v>
+        <v>533994</v>
       </c>
       <c r="R12" t="n">
-        <v>6596110</v>
+        <v>6596007</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125847854</v>
+        <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58374</v>
+        <v>58334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533952</v>
+        <v>534002</v>
       </c>
       <c r="R13" t="n">
-        <v>6596094</v>
+        <v>6596110</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>125847639</v>
       </c>
       <c r="B15" t="n">
-        <v>57830</v>
+        <v>57909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>125847639</v>
       </c>
       <c r="B15" t="n">
-        <v>57909</v>
+        <v>57910</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>125847639</v>
       </c>
       <c r="B15" t="n">
-        <v>57910</v>
+        <v>57913</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>125847639</v>
       </c>
       <c r="B15" t="n">
-        <v>57913</v>
+        <v>57914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1483,12 +1483,7 @@
         <v>123520087</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1592,7 @@
         <v>125847855</v>
       </c>
       <c r="B10" t="n">
-        <v>58027</v>
+        <v>58224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1834,7 @@
         <v>125848524</v>
       </c>
       <c r="B12" t="n">
-        <v>58195</v>
+        <v>58393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2081,7 +2076,7 @@
         <v>125847641</v>
       </c>
       <c r="B14" t="n">
-        <v>58027</v>
+        <v>58224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1483,7 +1483,7 @@
         <v>123520087</v>
       </c>
       <c r="B9" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>125847855</v>
       </c>
       <c r="B10" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>125848524</v>
       </c>
       <c r="B12" t="n">
-        <v>58393</v>
+        <v>58395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>125847641</v>
       </c>
       <c r="B14" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58605</v>
+        <v>58607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58607</v>
+        <v>58608</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58567</v>
+        <v>58568</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58568</v>
+        <v>58569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58609</v>
+        <v>58612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58569</v>
+        <v>58572</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58612</v>
+        <v>58613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58572</v>
+        <v>58573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58613</v>
+        <v>58619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58573</v>
+        <v>58579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58619</v>
+        <v>58620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58579</v>
+        <v>58580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58620</v>
+        <v>58623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58580</v>
+        <v>58583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Berg, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>125847854</v>
       </c>
       <c r="B11" t="n">
-        <v>58623</v>
+        <v>58625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125848529</v>
       </c>
       <c r="B13" t="n">
-        <v>58583</v>
+        <v>58585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121353385</v>
+        <v>125847639</v>
       </c>
       <c r="B2" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>102623</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boängen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533928</v>
+        <v>533992</v>
       </c>
       <c r="R2" t="n">
-        <v>6595955</v>
+        <v>6596062</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,78 +784,74 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Tufvesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Rejlers - NVI solpark Lindesberg</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121353379</v>
+        <v>125848524</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boängen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533913</v>
+        <v>533994</v>
       </c>
       <c r="R3" t="n">
-        <v>6596115</v>
+        <v>6596007</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,78 +905,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Rejlers - NVI solpark Lindesberg</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353383</v>
+        <v>123520087</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Boängen, Vstm</t>
+          <t>Nybo, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533918</v>
+        <v>533966</v>
       </c>
       <c r="R4" t="n">
-        <v>6596093</v>
+        <v>6596184</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,31 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Tufvesson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Rejlers - NVI solpark Lindesberg</t>
-        </is>
-      </c>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353384</v>
+        <v>125847641</v>
       </c>
       <c r="B5" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,46 +1037,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Boängen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533894</v>
+        <v>533982</v>
       </c>
       <c r="R5" t="n">
-        <v>6596085</v>
+        <v>6596121</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1105,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,53 +1135,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Tufvesson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Rejlers - NVI solpark Lindesberg</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353380</v>
+        <v>125847855</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1173,24 +1180,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Boängen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533928</v>
+        <v>533951</v>
       </c>
       <c r="R6" t="n">
-        <v>6596116</v>
+        <v>6596095</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,12 +1226,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,31 +1256,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Rejlers - NVI solpark Lindesberg</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353381</v>
+        <v>125848529</v>
       </c>
       <c r="B7" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,24 +1301,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nybo, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533977</v>
+        <v>534002</v>
       </c>
       <c r="R7" t="n">
-        <v>6596107</v>
+        <v>6596110</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,12 +1347,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,78 +1377,74 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Rejlers - NVI solpark Lindesberg</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353382</v>
+        <v>125847854</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybo, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533939</v>
+        <v>533952</v>
       </c>
       <c r="R8" t="n">
-        <v>6596125</v>
+        <v>6596094</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,12 +1468,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,76 +1498,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Tufvesson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Rejlers - NVI solpark Lindesberg</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123520087</v>
+        <v>121353379</v>
       </c>
       <c r="B9" t="n">
-        <v>58256</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nybo, Vstm</t>
+          <t>Boängen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533966</v>
+        <v>533913</v>
       </c>
       <c r="R9" t="n">
-        <v>6596184</v>
+        <v>6596115</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,12 +1584,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,44 +1604,48 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Diana Rubene</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI solpark Lindesberg</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125847855</v>
+        <v>121353380</v>
       </c>
       <c r="B10" t="n">
-        <v>58256</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1622,29 +1653,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Boängen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533951</v>
+        <v>533928</v>
       </c>
       <c r="R10" t="n">
-        <v>6596095</v>
+        <v>6596116</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,22 +1694,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>07:12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>07:12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,74 +1714,73 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Diana Rubene</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI solpark Lindesberg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125847854</v>
+        <v>121353382</v>
       </c>
       <c r="B11" t="n">
-        <v>58625</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Nybo, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533952</v>
+        <v>533939</v>
       </c>
       <c r="R11" t="n">
-        <v>6596094</v>
+        <v>6596125</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,22 +1804,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>07:12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>07:12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,74 +1824,73 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Kristian Tufvesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI solpark Lindesberg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125848524</v>
+        <v>121353383</v>
       </c>
       <c r="B12" t="n">
-        <v>58425</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Boängen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533994</v>
+        <v>533918</v>
       </c>
       <c r="R12" t="n">
-        <v>6596007</v>
+        <v>6596093</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,22 +1914,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>07:21</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>07:21</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,22 +1934,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Kristian Tufvesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI solpark Lindesberg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125848529</v>
+        <v>121353381</v>
       </c>
       <c r="B13" t="n">
-        <v>58585</v>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1961,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1985,29 +1983,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Nybo, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534002</v>
+        <v>533977</v>
       </c>
       <c r="R13" t="n">
-        <v>6596110</v>
+        <v>6596107</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,22 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>07:18</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>07:18</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,22 +2044,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Diana Rubene</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI solpark Lindesberg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125847641</v>
+        <v>121353384</v>
       </c>
       <c r="B14" t="n">
-        <v>58256</v>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,51 +2071,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Boängen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533982</v>
+        <v>533894</v>
       </c>
       <c r="R14" t="n">
-        <v>6596121</v>
+        <v>6596085</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2152,22 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:33</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:33</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,22 +2154,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Kristian Tufvesson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI solpark Lindesberg</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125847639</v>
+        <v>121353385</v>
       </c>
       <c r="B15" t="n">
-        <v>57915</v>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,21 +2181,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102623</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2227,29 +2203,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Boängen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533992</v>
+        <v>533928</v>
       </c>
       <c r="R15" t="n">
-        <v>6596062</v>
+        <v>6595955</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2273,22 +2244,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:35</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:35</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,15 +2264,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Erik Berg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Kristian Tufvesson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI solpark Lindesberg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26749-2025 artfynd.xlsx
+++ b/artfynd/A 26749-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125847639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125848524</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123520087</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125847641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125847855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125848529</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1507,6 +1542,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125847854</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1617,6 +1657,11 @@
           <t>Rejlers - NVI solpark Lindesberg</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121353379</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1727,6 +1772,11 @@
           <t>Rejlers - NVI solpark Lindesberg</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121353380</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
           <t>Rejlers - NVI solpark Lindesberg</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121353382</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1947,6 +2002,11 @@
           <t>Rejlers - NVI solpark Lindesberg</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121353383</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2057,6 +2117,11 @@
           <t>Rejlers - NVI solpark Lindesberg</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121353381</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
           <t>Rejlers - NVI solpark Lindesberg</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121353384</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,8 +2347,29 @@
           <t>Rejlers - NVI solpark Lindesberg</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121353385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>